--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25AD8F85-F324-485B-BD97-63E50F936577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564EEED0-F28B-4C4F-87E7-87FF8ABFBE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Dev Work Log</t>
+  </si>
+  <si>
+    <t>Standardised new refactoring across all weapon behaviour. Many bugs, attempting to address bugs.</t>
   </si>
 </sst>
 </file>
@@ -149,8 +152,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A4:E6" totalsRowShown="0">
-  <autoFilter ref="A4:E6" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A4:E8" totalsRowShown="0">
+  <autoFilter ref="A4:E8" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="1"/>
@@ -479,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -538,6 +541,31 @@
       <c r="B6" s="2">
         <v>0.87013888888888891</v>
       </c>
+      <c r="C6" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45739</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>0.70833333333333337</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{564EEED0-F28B-4C4F-87E7-87FF8ABFBE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E71DCC-7BDC-4B35-981B-68E73C7B3CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -66,6 +66,15 @@
   </si>
   <si>
     <t>Standardised new refactoring across all weapon behaviour. Many bugs, attempting to address bugs.</t>
+  </si>
+  <si>
+    <t>Refactoring complete (still not as refactored as much as would like as projectile.gd still handles more than I would really like, but in interest of moving forward am making do with what we have for now). Now trouble fixing bugs in how projectiles are behaving. Fixed homing, fixed cluster bomb, currently fixing bounce orb (not bouncing)</t>
+  </si>
+  <si>
+    <t>Total hours:</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
@@ -131,7 +140,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -152,14 +164,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A4:E8" totalsRowShown="0">
-  <autoFilter ref="A4:E8" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A6:F11" totalsRowShown="0">
+  <autoFilter ref="A6:F11" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{385CF12C-F475-4237-A1B1-BA2B136D502D}" name="Finish"/>
     <tableColumn id="4" xr3:uid="{A53CF1BF-F8B6-4BD3-8E81-2C1B7E645EAD}" name="Task"/>
-    <tableColumn id="5" xr3:uid="{82A06DB5-D5A5-417C-9A3D-8CC5431A3DD7}" name="Details" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{82A06DB5-D5A5-417C-9A3D-8CC5431A3DD7}" name="Details" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{6B5828D5-4B73-426F-9AEB-9B2280524C8F}" name="Time" dataDxfId="0">
+      <calculatedColumnFormula>IF(C7&lt;B7, C7+1, C7) - B7</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -482,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -491,80 +506,135 @@
     <col min="5" max="5" width="47.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:5" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <f>SUM(F7:F37)</f>
+        <v>0.5180555555555556</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C6" t="s">
         <v>4</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>45738</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B7" s="2">
         <v>0.625</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C7" s="2">
         <v>0.77430555555555558</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
-        <v>0.87013888888888891</v>
-      </c>
-      <c r="C6" s="2">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>45739</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.5625</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" ref="F7:F11" si="0">IF(C7&lt;B7, C7+1, C7) - B7</f>
+        <v>0.14930555555555558</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>0.87013888888888891</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17152777777777783</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45739</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
-        <v>0.70833333333333337</v>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.88472222222222219</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>9.3055555555555558E-2</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
+        <v>4.166666666666663E-2</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E71DCC-7BDC-4B35-981B-68E73C7B3CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B037CD74-5A6C-4D48-BDCA-C46A72A74AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView minimized="1" xWindow="3120" yWindow="3120" windowWidth="15030" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
+    <sheet name="Godot Learning" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -75,6 +76,21 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>Fixed bugs in all projectile weapons (apart from those which are down to preference and want to make better/different)</t>
+  </si>
+  <si>
+    <t>Godot Learning</t>
+  </si>
+  <si>
+    <t>Dev Practice Log</t>
+  </si>
+  <si>
+    <t>Refactoring projectile system and improving behaviour system</t>
+  </si>
+  <si>
+    <t>Ask whether references to "improved_behaviour_manager" or just behaviour manager etc</t>
   </si>
 </sst>
 </file>
@@ -140,7 +156,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
     </dxf>
@@ -164,15 +189,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A6:F11" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A6:F12" totalsRowShown="0">
+  <autoFilter ref="A6:F12" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
+    <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{385CF12C-F475-4237-A1B1-BA2B136D502D}" name="Finish"/>
+    <tableColumn id="4" xr3:uid="{A53CF1BF-F8B6-4BD3-8E81-2C1B7E645EAD}" name="Task"/>
+    <tableColumn id="5" xr3:uid="{82A06DB5-D5A5-417C-9A3D-8CC5431A3DD7}" name="Details" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{6B5828D5-4B73-426F-9AEB-9B2280524C8F}" name="Time" dataDxfId="3">
+      <calculatedColumnFormula>IF(C7&lt;B7, C7+1, C7) - B7</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7A4A6574-3FF0-4809-85FD-1DDCB83EA4DD}" name="Table22" displayName="Table22" ref="A6:F11" totalsRowShown="0">
   <autoFilter ref="A6:F11" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{385CF12C-F475-4237-A1B1-BA2B136D502D}" name="Finish"/>
-    <tableColumn id="4" xr3:uid="{A53CF1BF-F8B6-4BD3-8E81-2C1B7E645EAD}" name="Task"/>
-    <tableColumn id="5" xr3:uid="{82A06DB5-D5A5-417C-9A3D-8CC5431A3DD7}" name="Details" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{6B5828D5-4B73-426F-9AEB-9B2280524C8F}" name="Time" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{79650798-B691-458A-BE4A-5916DBAC4166}" name="Date"/>
+    <tableColumn id="2" xr3:uid="{064DF555-2569-4B26-8250-62634D76A69A}" name="Start" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{20620684-1ED7-4B49-B03F-DD32723B4EEF}" name="Finish"/>
+    <tableColumn id="4" xr3:uid="{82FD299F-7E84-4584-8794-9F819C3DD798}" name="Task"/>
+    <tableColumn id="5" xr3:uid="{C4AAFEC7-694F-42A2-A652-7DBB66C273C0}" name="Details" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{3FF97942-C807-4B84-B488-6C3FE6D21D35}" name="Time" dataDxfId="0">
       <calculatedColumnFormula>IF(C7&lt;B7, C7+1, C7) - B7</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -497,6 +539,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.42578125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="5"/>
+    </row>
+    <row r="2" spans="1:12" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2">
+        <f>SUM(F7:F37)</f>
+        <v>1.0319444444444446</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="L6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" ref="F7:F11" si="0">IF(C7&lt;B7, C7+1, C7) - B7</f>
+        <v>0.14930555555555558</v>
+      </c>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>0.87013888888888891</v>
+      </c>
+      <c r="C8" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17152777777777783</v>
+      </c>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45739</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.88472222222222219</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>9.3055555555555558E-2</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="B11" s="2">
+        <v>0.97430555555555554</v>
+      </c>
+      <c r="C11" s="2">
+        <v>7.1527777777777773E-2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
+        <v>9.7222222222222321E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45740</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2">
+        <f>IF(C12&lt;B12, C12+1, C12) - B12</f>
+        <v>0.45833333333333337</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16EBAB43-9BF7-46C1-BE2D-33751923E718}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -508,13 +728,13 @@
   <sheetData>
     <row r="1" spans="1:8" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E1" s="5"/>
     </row>
     <row r="2" spans="1:8" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E2" s="5"/>
     </row>
@@ -524,7 +744,7 @@
       </c>
       <c r="C4" s="2">
         <f>SUM(F7:F37)</f>
-        <v>0.5180555555555556</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2"/>
     </row>
@@ -552,89 +772,50 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>45738</v>
-      </c>
-      <c r="B7" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0.77430555555555558</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>2</v>
-      </c>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
       <c r="F7" s="2">
         <f t="shared" ref="F7:F11" si="0">IF(C7&lt;B7, C7+1, C7) - B7</f>
-        <v>0.14930555555555558</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
-        <v>0.87013888888888891</v>
-      </c>
-      <c r="C8" s="2">
-        <v>4.1666666666666664E-2</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
       <c r="F8" s="2">
         <f t="shared" si="0"/>
-        <v>0.17152777777777783</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>45739</v>
-      </c>
-      <c r="B9" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
       <c r="F9" s="2">
         <f t="shared" si="0"/>
-        <v>6.25E-2</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.88472222222222219</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>10</v>
-      </c>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
       <c r="F10" s="2">
         <f t="shared" si="0"/>
-        <v>9.3055555555555558E-2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
-        <v>0.95833333333333337</v>
-      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
       <c r="F11" s="2">
         <f t="shared" si="0"/>
-        <v>4.166666666666663E-2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B037CD74-5A6C-4D48-BDCA-C46A72A74AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD392ED7-29D1-41E9-A67D-20A1E721591D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3120" yWindow="3120" windowWidth="15030" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -91,6 +91,17 @@
   </si>
   <si>
     <t>Ask whether references to "improved_behaviour_manager" or just behaviour manager etc</t>
+  </si>
+  <si>
+    <t>Brackeys Tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting from scratch
+- animatable body2d (for moving objects you want to collide with, e.g. platform)
+- enabled one-way collision in transport so player can jump from below
+- animated spite2d (for player character)
+-collision shape 2d (for player collision)
+</t>
   </si>
 </sst>
 </file>
@@ -566,7 +577,7 @@
       </c>
       <c r="C4" s="2">
         <f>SUM(F7:F37)</f>
-        <v>1.0319444444444446</v>
+        <v>0.71944444444444466</v>
       </c>
       <c r="H4" s="2"/>
     </row>
@@ -698,12 +709,15 @@
       <c r="B12" s="2">
         <v>0.54166666666666663</v>
       </c>
+      <c r="C12" s="2">
+        <v>0.6875</v>
+      </c>
       <c r="E12" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F12" s="2">
         <f>IF(C12&lt;B12, C12+1, C12) - B12</f>
-        <v>0.45833333333333337</v>
+        <v>0.14583333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -744,7 +758,7 @@
       </c>
       <c r="C4" s="2">
         <f>SUM(F7:F37)</f>
-        <v>0</v>
+        <v>2.083333333333337E-2</v>
       </c>
       <c r="H4" s="2"/>
     </row>
@@ -772,13 +786,25 @@
       </c>
       <c r="H6" s="2"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+    <row r="7" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45740</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="F7" s="2">
         <f t="shared" ref="F7:F11" si="0">IF(C7&lt;B7, C7+1, C7) - B7</f>
-        <v>0</v>
+        <v>2.083333333333337E-2</v>
       </c>
       <c r="H7" s="2"/>
     </row>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD392ED7-29D1-41E9-A67D-20A1E721591D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163803CD-1F74-4B04-BAE8-186E10E3627F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -88,9 +88,6 @@
   </si>
   <si>
     <t>Refactoring projectile system and improving behaviour system</t>
-  </si>
-  <si>
-    <t>Ask whether references to "improved_behaviour_manager" or just behaviour manager etc</t>
   </si>
   <si>
     <t>Brackeys Tutorial</t>
@@ -102,6 +99,10 @@
 - animated spite2d (for player character)
 -collision shape 2d (for player collision)
 </t>
+  </si>
+  <si>
+    <t>Refactoring system complete. Bug fixes for weapons.
+Annoying 'indent' issue, hoping just needed a close and restart, will test tomorrow.</t>
   </si>
 </sst>
 </file>
@@ -200,8 +201,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A6:F12" totalsRowShown="0">
-  <autoFilter ref="A6:F12" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A6:F13" totalsRowShown="0">
+  <autoFilter ref="A6:F13" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
@@ -550,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -559,32 +560,32 @@
     <col min="5" max="5" width="47.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:12" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(F7:F37)</f>
-        <v>0.71944444444444466</v>
+        <v>0.7958333333333335</v>
       </c>
       <c r="H4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="H5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -604,11 +605,8 @@
         <v>12</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="L6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>45738</v>
       </c>
@@ -630,7 +628,7 @@
       </c>
       <c r="H7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" s="2">
         <v>0.87013888888888891</v>
       </c>
@@ -643,7 +641,7 @@
       </c>
       <c r="H8" s="2"/>
     </row>
-    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>45739</v>
       </c>
@@ -665,7 +663,7 @@
       </c>
       <c r="H9" s="2"/>
     </row>
-    <row r="10" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>0.79166666666666663</v>
       </c>
@@ -684,7 +682,7 @@
       </c>
       <c r="H10" s="2"/>
     </row>
-    <row r="11" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>0.97430555555555554</v>
       </c>
@@ -702,7 +700,7 @@
         <v>9.7222222222222321E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>45740</v>
       </c>
@@ -711,6 +709,9 @@
       </c>
       <c r="C12" s="2">
         <v>0.6875</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>16</v>
@@ -718,6 +719,24 @@
       <c r="F12" s="2">
         <f>IF(C12&lt;B12, C12+1, C12) - B12</f>
         <v>0.14583333333333337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="C13" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2">
+        <f>IF(C13&lt;B13, C13+1, C13) - B13</f>
+        <v>7.638888888888884E-2</v>
       </c>
     </row>
   </sheetData>
@@ -797,10 +816,10 @@
         <v>0.9375</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" ref="F7:F11" si="0">IF(C7&lt;B7, C7+1, C7) - B7</f>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163803CD-1F74-4B04-BAE8-186E10E3627F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893C9328-9735-4328-8EAD-02A688DA494A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -104,11 +104,24 @@
     <t>Refactoring system complete. Bug fixes for weapons.
 Annoying 'indent' issue, hoping just needed a close and restart, will test tomorrow.</t>
   </si>
+  <si>
+    <t>Cleaning up refactored system.
+- Added null refernces to behaviour manager
+- Addressing missed signal connections
+- Addressing timer managerment problems
+- Physics and movement issues</t>
+  </si>
+  <si>
+    <t>Fixing bugs with all weapons. Not very happy with how much weapons have all changed, but hopefully continual bug fixing will end up with a more resiliant system once done.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[h]:mm"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -152,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -164,6 +177,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -201,8 +215,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="A6:F13" totalsRowShown="0">
-  <autoFilter ref="A6:F13" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G15" totalsRowShown="0">
+  <autoFilter ref="B6:G15" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
@@ -210,7 +224,7 @@
     <tableColumn id="4" xr3:uid="{A53CF1BF-F8B6-4BD3-8E81-2C1B7E645EAD}" name="Task"/>
     <tableColumn id="5" xr3:uid="{82A06DB5-D5A5-417C-9A3D-8CC5431A3DD7}" name="Details" dataDxfId="4"/>
     <tableColumn id="6" xr3:uid="{6B5828D5-4B73-426F-9AEB-9B2280524C8F}" name="Time" dataDxfId="3">
-      <calculatedColumnFormula>IF(C7&lt;B7, C7+1, C7) - B7</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(D7&lt;C7, D7+1, D7) - C7</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -551,192 +565,231 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+      <c r="F2" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2">
-        <f>SUM(F7:F37)</f>
-        <v>0.7958333333333335</v>
-      </c>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="D4" s="7">
+        <f>SUM(G7:G37)</f>
+        <v>1.0319444444444446</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>4</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
         <v>45738</v>
       </c>
-      <c r="B7" s="2">
+      <c r="C7" s="2">
         <v>0.625</v>
       </c>
-      <c r="C7" s="2">
+      <c r="D7" s="2">
         <v>0.77430555555555558</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="2">
-        <f t="shared" ref="F7:F11" si="0">IF(C7&lt;B7, C7+1, C7) - B7</f>
+      <c r="G7" s="2">
+        <f t="shared" ref="G7:G11" si="0">IF(D7&lt;C7, D7+1, D7) - C7</f>
         <v>0.14930555555555558</v>
       </c>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="2">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C8" s="2">
         <v>0.87013888888888891</v>
       </c>
-      <c r="C8" s="2">
+      <c r="D8" s="2">
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <f t="shared" si="0"/>
         <v>0.17152777777777783</v>
       </c>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="1">
         <v>45739</v>
       </c>
-      <c r="B9" s="2">
+      <c r="C9" s="2">
         <v>0.5</v>
       </c>
-      <c r="C9" s="2">
+      <c r="D9" s="2">
         <v>0.5625</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="C10" s="2">
         <v>0.79166666666666663</v>
       </c>
-      <c r="C10" s="2">
+      <c r="D10" s="2">
         <v>0.88472222222222219</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>1</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G10" s="2">
         <f t="shared" si="0"/>
         <v>9.3055555555555558E-2</v>
       </c>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" ht="45" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="C11" s="2">
         <v>0.97430555555555554</v>
       </c>
-      <c r="C11" s="2">
+      <c r="D11" s="2">
         <v>7.1527777777777773E-2</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>1</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G11" s="2">
         <f t="shared" si="0"/>
         <v>9.7222222222222321E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
         <v>45740</v>
       </c>
-      <c r="B12" s="2">
+      <c r="C12" s="2">
         <v>0.54166666666666663</v>
       </c>
-      <c r="C12" s="2">
+      <c r="D12" s="2">
         <v>0.6875</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="2">
-        <f>IF(C12&lt;B12, C12+1, C12) - B12</f>
+      <c r="G12" s="2">
+        <f>IF(D12&lt;C12, D12+1, D12) - C12</f>
         <v>0.14583333333333337</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
+    <row r="13" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="C13" s="2">
         <v>0.98611111111111116</v>
       </c>
-      <c r="C13" s="2">
+      <c r="D13" s="2">
         <v>6.25E-2</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>1</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="2">
-        <f>IF(C13&lt;B13, C13+1, C13) - B13</f>
+      <c r="G13" s="2">
+        <f>IF(D13&lt;C13, D13+1, D13) - C13</f>
         <v>7.638888888888884E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>45741</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="2">
+        <f>IF(D14&lt;C14, D14+1, D14) - C14</f>
+        <v>0.15277777777777779</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="C15" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="2">
+        <f>IF(D15&lt;C15, D15+1, D15) - C15</f>
+        <v>8.3333333333333259E-2</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893C9328-9735-4328-8EAD-02A688DA494A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F371EE69-A42B-426C-8C55-77087561231B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -114,13 +114,20 @@
   <si>
     <t>Fixing bugs with all weapons. Not very happy with how much weapons have all changed, but hopefully continual bug fixing will end up with a more resiliant system once done.</t>
   </si>
+  <si>
+    <t>Tidied up the following:
+- Fixed Signal Safety Issues – Ensured all signals were properly connected and disconnected. 
+- Fixed Behavior Application – Made sure behaviors were correctly applied to projectiles. 
+- Implemented Safe Metadata Access – Added checks before accessing metadata.
+- Added Null Reference Checks – Protected against null reference exceptions.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[h]:mm"/>
+    <numFmt numFmtId="164" formatCode="[h]:mm"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -177,7 +184,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -215,8 +222,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G15" totalsRowShown="0">
-  <autoFilter ref="B6:G15" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G20" totalsRowShown="0">
+  <autoFilter ref="B6:G20" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
@@ -565,7 +572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -591,8 +598,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G37)</f>
-        <v>1.0319444444444446</v>
+        <f>SUM(G7:G41)</f>
+        <v>1.1361111111111111</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -790,6 +797,63 @@
       <c r="G15" s="2">
         <f>IF(D15&lt;C15, D15+1, D15) - C15</f>
         <v>8.3333333333333259E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <v>45742</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="2">
+        <f>IF(D16&lt;C16, D16+1, D16) - C16</f>
+        <v>0.10416666666666663</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="G17" s="2">
+        <f t="shared" ref="G17:G20" si="1">IF(D17&lt;C17, D17+1, D17) - C17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="G18" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="G19" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="G20" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F371EE69-A42B-426C-8C55-77087561231B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65E6C48-1CDC-4150-BD80-A1BB4AFB5C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -120,6 +120,15 @@
 - Fixed Behavior Application – Made sure behaviors were correctly applied to projectiles. 
 - Implemented Safe Metadata Access – Added checks before accessing metadata.
 - Added Null Reference Checks – Protected against null reference exceptions.</t>
+  </si>
+  <si>
+    <t>Fixing singularity bomb</t>
+  </si>
+  <si>
+    <t>Fixed singularity
+Fixed bounce orb
+Added wild bounce orb
+Started working on cluster bomb</t>
   </si>
 </sst>
 </file>
@@ -599,7 +608,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>1.1361111111111111</v>
+        <v>1.6152777777777776</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -821,30 +830,64 @@
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="1"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
+      <c r="B17" s="1">
+        <v>45744</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G17" s="2">
         <f t="shared" ref="G17:G20" si="1">IF(D17&lt;C17, D17+1, D17) - C17</f>
-        <v>0</v>
+        <v>0.25000000000000011</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="1">
+        <v>45745</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G18" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>6.2500000000000056E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
+      <c r="C19" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="G19" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.16666666666666663</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65E6C48-1CDC-4150-BD80-A1BB4AFB5C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC31BCD0-4908-46ED-BA7D-6135842E7A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -129,6 +129,16 @@
 Fixed bounce orb
 Added wild bounce orb
 Started working on cluster bomb</t>
+  </si>
+  <si>
+    <t>Fixing cluster bomb</t>
+  </si>
+  <si>
+    <t>Fixing cluster bomb
+- created new cluster bomb behavior
+- created new arc behavior
+- created new explosion behavior
+- created new multishot behavior</t>
   </si>
 </sst>
 </file>
@@ -231,8 +241,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G20" totalsRowShown="0">
-  <autoFilter ref="B6:G20" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G22" totalsRowShown="0">
+  <autoFilter ref="B6:G22" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
@@ -581,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -608,7 +618,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>1.6152777777777776</v>
+        <v>2.34375</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -892,11 +902,54 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="C20" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="G20" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C21" s="2">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="2">
+        <f>IF(D21&lt;C21, D21+1, D21) - C21</f>
+        <v>5.208333333333337E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="B22" s="1">
+        <v>45746</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.61388888888888893</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="2">
+        <f>IF(D22&lt;C22, D22+1, D22) - C22</f>
+        <v>0.11388888888888893</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC31BCD0-4908-46ED-BA7D-6135842E7A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1EFB10-DFDA-4B58-B3A6-99035AE40B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -139,6 +139,20 @@
 - created new arc behavior
 - created new explosion behavior
 - created new multishot behavior</t>
+  </si>
+  <si>
+    <t>Trying to fix behavior manager to parse new behaviors</t>
+  </si>
+  <si>
+    <t>Tried using bezier behavior instead of arc for falling curve
+- Created new BezierBehavior
+- Updated multishot to try to give individual arcs
+- Troubleshooting bezier behavior</t>
+  </si>
+  <si>
+    <t>Fixed Cluster bomb/bezier behavior
+- exploring how to adjust parameters in script
+- question over how these changes to parameters could be utilised in weapon data</t>
   </si>
 </sst>
 </file>
@@ -241,8 +255,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G22" totalsRowShown="0">
-  <autoFilter ref="B6:G22" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G25" totalsRowShown="0">
+  <autoFilter ref="B6:G25" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
@@ -591,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -618,7 +632,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>2.34375</v>
+        <v>2.5347222222222223</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -950,6 +964,60 @@
       <c r="G22" s="2">
         <f>IF(D22&lt;C22, D22+1, D22) - C22</f>
         <v>0.11388888888888893</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="C23" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.85763888888888884</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="2">
+        <f>IF(D23&lt;C23, D23+1, D23) - C23</f>
+        <v>6.597222222222221E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="B24" s="1">
+        <v>45747</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="2">
+        <f>IF(D24&lt;C24, D24+1, D24) - C24</f>
+        <v>9.375E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="C25" s="2">
+        <v>0.75902777777777775</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="2">
+        <f>IF(D25&lt;C25, D25+1, D25) - C25</f>
+        <v>3.125E-2</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1EFB10-DFDA-4B58-B3A6-99035AE40B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596AAB39-DB6D-467A-BB4B-5AF3CC8DBBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -153,6 +153,15 @@
     <t>Fixed Cluster bomb/bezier behavior
 - exploring how to adjust parameters in script
 - question over how these changes to parameters could be utilised in weapon data</t>
+  </si>
+  <si>
+    <t>Fixed cluster bomb/bezier behavior and adapted bezier to be able to accommodate mutiple projectiles (not just 3)</t>
+  </si>
+  <si>
+    <t>Trying to fix shotgun with updates to mutishot and projectile_attack_style but questions over whether this will disrupt new bezier</t>
+  </si>
+  <si>
+    <t>Attempting to fix shotgun</t>
   </si>
 </sst>
 </file>
@@ -255,8 +264,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G25" totalsRowShown="0">
-  <autoFilter ref="B6:G25" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G29" totalsRowShown="0">
+  <autoFilter ref="B6:G29" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
@@ -605,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -632,7 +641,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>2.5347222222222223</v>
+        <v>2.7256944444444446</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -941,7 +950,7 @@
         <v>25</v>
       </c>
       <c r="G21" s="2">
-        <f>IF(D21&lt;C21, D21+1, D21) - C21</f>
+        <f t="shared" ref="G21:G27" si="2">IF(D21&lt;C21, D21+1, D21) - C21</f>
         <v>5.208333333333337E-2</v>
       </c>
     </row>
@@ -962,7 +971,7 @@
         <v>26</v>
       </c>
       <c r="G22" s="2">
-        <f>IF(D22&lt;C22, D22+1, D22) - C22</f>
+        <f t="shared" si="2"/>
         <v>0.11388888888888893</v>
       </c>
     </row>
@@ -977,7 +986,7 @@
         <v>27</v>
       </c>
       <c r="G23" s="2">
-        <f>IF(D23&lt;C23, D23+1, D23) - C23</f>
+        <f t="shared" si="2"/>
         <v>6.597222222222221E-2</v>
       </c>
     </row>
@@ -998,7 +1007,7 @@
         <v>28</v>
       </c>
       <c r="G24" s="2">
-        <f>IF(D24&lt;C24, D24+1, D24) - C24</f>
+        <f t="shared" si="2"/>
         <v>9.375E-2</v>
       </c>
     </row>
@@ -1016,8 +1025,83 @@
         <v>29</v>
       </c>
       <c r="G25" s="2">
-        <f>IF(D25&lt;C25, D25+1, D25) - C25</f>
+        <f t="shared" si="2"/>
         <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="C26" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.98263888888888884</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="2"/>
+        <v>8.6805555555555469E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="C27" s="2">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="2"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="1">
+        <v>45749</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="2">
+        <f>IF(D28&lt;C28, D28+1, D28) - C28</f>
+        <v>3.472222222222221E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1">
+        <v>45750</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.96180555555555558</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29" s="2">
+        <f>IF(D29&lt;C29, D29+1, D29) - C29</f>
+        <v>3.819444444444442E-2</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{596AAB39-DB6D-467A-BB4B-5AF3CC8DBBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C508A0-34E2-465D-9D10-4EB3ACF03866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -162,6 +162,14 @@
   </si>
   <si>
     <t>Attempting to fix shotgun</t>
+  </si>
+  <si>
+    <t>Fixed shotgun and tested most weapons
+- Need to re-fix singularity after adding bexier arc
+- Most weapons functioning
+- Need more differentation (although perhaps damage stats will help)
+- Need to build documentation to detail parameters and how to change them
+- Potentially try adding more new behaviors</t>
   </si>
 </sst>
 </file>
@@ -641,7 +649,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>2.7256944444444446</v>
+        <v>2.7631944444444443</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1086,22 +1094,25 @@
         <v>3.472222222222221E-2</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" ht="120" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>45750</v>
       </c>
       <c r="C29" s="2">
         <v>0.96180555555555558</v>
       </c>
+      <c r="D29" s="2">
+        <v>3.7499999999999999E-2</v>
+      </c>
       <c r="E29" t="s">
         <v>1</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G29" s="2">
         <f>IF(D29&lt;C29, D29+1, D29) - C29</f>
-        <v>3.819444444444442E-2</v>
+        <v>7.5694444444444509E-2</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C508A0-34E2-465D-9D10-4EB3ACF03866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5793A7E4-9776-4624-AA2E-FC4543E4D2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -164,12 +164,19 @@
     <t>Attempting to fix shotgun</t>
   </si>
   <si>
+    <t>Fixed Singularity
+- Fixed pull blade</t>
+  </si>
+  <si>
     <t>Fixed shotgun and tested most weapons
-- Need to re-fix singularity after adding bexier arc
+- Need to re-fix singularity after adding bezier arc
 - Most weapons functioning
 - Need more differentation (although perhaps damage stats will help)
 - Need to build documentation to detail parameters and how to change them
 - Potentially try adding more new behaviors</t>
+  </si>
+  <si>
+    <t>Added 'dagger' attack style, and started implementing 'cooldown' behavior, with meter. But cooldown and next attack don't quite seem in-line. Want to find way to make input more immediate, natural</t>
   </si>
 </sst>
 </file>
@@ -272,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G29" totalsRowShown="0">
-  <autoFilter ref="B6:G29" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G31" totalsRowShown="0">
+  <autoFilter ref="B6:G31" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
@@ -622,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -649,7 +656,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>2.7631944444444443</v>
+        <v>2.8319444444444444</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1108,11 +1115,50 @@
         <v>1</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G29" s="2">
         <f>IF(D29&lt;C29, D29+1, D29) - C29</f>
         <v>7.5694444444444509E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B30" s="1">
+        <v>45751</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.72569444444444442</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="2">
+        <f>IF(D30&lt;C30, D30+1, D30) - C30</f>
+        <v>3.819444444444442E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="C31" s="2">
+        <v>0.88124999999999998</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.91180555555555554</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="2">
+        <f>IF(D31&lt;C31, D31+1, D31) - C31</f>
+        <v>3.0555555555555558E-2</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5793A7E4-9776-4624-AA2E-FC4543E4D2B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50B785D-F2AD-4D3D-BEFC-44301D603F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="37">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -177,6 +177,9 @@
   </si>
   <si>
     <t>Added 'dagger' attack style, and started implementing 'cooldown' behavior, with meter. But cooldown and next attack don't quite seem in-line. Want to find way to make input more immediate, natural</t>
+  </si>
+  <si>
+    <t>Fixing cooldown</t>
   </si>
 </sst>
 </file>
@@ -279,8 +282,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G31" totalsRowShown="0">
-  <autoFilter ref="B6:G31" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G32" totalsRowShown="0">
+  <autoFilter ref="B6:G32" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
@@ -629,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -656,7 +659,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>2.8319444444444444</v>
+        <v>3.2833333333333332</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1159,6 +1162,24 @@
       <c r="G31" s="2">
         <f>IF(D31&lt;C31, D31+1, D31) - C31</f>
         <v>3.0555555555555558E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="1">
+        <v>45752</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="2">
+        <f>IF(D32&lt;C32, D32+1, D32) - C32</f>
+        <v>0.45138888888888884</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50B785D-F2AD-4D3D-BEFC-44301D603F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78873092-0864-4483-A329-02093806C1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="1560" yWindow="735" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
-    <sheet name="Godot Learning" sheetId="2" r:id="rId2"/>
+    <sheet name="Card Combiner" sheetId="3" r:id="rId2"/>
+    <sheet name="Godot Learning" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -180,6 +181,22 @@
   </si>
   <si>
     <t>Fixing cooldown</t>
+  </si>
+  <si>
+    <t>Card Combiner</t>
+  </si>
+  <si>
+    <t>Basic Mechanic</t>
+  </si>
+  <si>
+    <t>Created scenes, nodes, scripts
+- created moveable buttons
+- started to implement recipes system
+- created cards and spawner</t>
+  </si>
+  <si>
+    <t>Fixed cooldown
+- Issues with certain weapons, e.g. singularity, fire staff</t>
   </si>
 </sst>
 </file>
@@ -249,7 +266,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="25" formatCode="hh:mm"/>
     </dxf>
@@ -282,15 +308,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G32" totalsRowShown="0">
-  <autoFilter ref="B6:G32" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G33" totalsRowShown="0">
+  <autoFilter ref="B6:G33" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{385CF12C-F475-4237-A1B1-BA2B136D502D}" name="Finish"/>
     <tableColumn id="4" xr3:uid="{A53CF1BF-F8B6-4BD3-8E81-2C1B7E645EAD}" name="Task"/>
-    <tableColumn id="5" xr3:uid="{82A06DB5-D5A5-417C-9A3D-8CC5431A3DD7}" name="Details" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{6B5828D5-4B73-426F-9AEB-9B2280524C8F}" name="Time" dataDxfId="3">
+    <tableColumn id="5" xr3:uid="{82A06DB5-D5A5-417C-9A3D-8CC5431A3DD7}" name="Details" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{6B5828D5-4B73-426F-9AEB-9B2280524C8F}" name="Time" dataDxfId="6">
       <calculatedColumnFormula>IF(D7&lt;C7, D7+1, D7) - C7</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -299,6 +325,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{AE49BDCB-9AE2-4D8E-9526-2EE8E335347E}" name="Table24" displayName="Table24" ref="B6:G32" totalsRowShown="0">
+  <autoFilter ref="B6:G32" xr:uid="{AE49BDCB-9AE2-4D8E-9526-2EE8E335347E}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{FAD75835-A4A6-4918-9A7C-99AF5B35770D}" name="Date"/>
+    <tableColumn id="2" xr3:uid="{F0977FC6-F5CF-465A-9207-1F73F89AE501}" name="Start" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{AD0BF73D-5F1F-45CA-8916-5DFA51120605}" name="Finish"/>
+    <tableColumn id="4" xr3:uid="{4BFA8C06-23BA-461E-9D77-82786B1054D2}" name="Task"/>
+    <tableColumn id="5" xr3:uid="{6A295F47-2BD5-4F2C-9493-8C28EB221635}" name="Details" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{59C01672-DED4-421F-882C-FE79042D7229}" name="Time" dataDxfId="3">
+      <calculatedColumnFormula>IF(D7&lt;C7, D7+1, D7) - C7</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7A4A6574-3FF0-4809-85FD-1DDCB83EA4DD}" name="Table22" displayName="Table22" ref="A6:F11" totalsRowShown="0">
   <autoFilter ref="A6:F11" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
@@ -632,6 +675,591 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.42578125" style="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:9" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7">
+        <f>SUM(G7:G41)</f>
+        <v>3.067361111111111</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
+        <v>45738</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.77430555555555558</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" ref="G7:G11" si="0">IF(D7&lt;C7, D7+1, D7) - C7</f>
+        <v>0.14930555555555558</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C8" s="2">
+        <v>0.87013888888888891</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17152777777777783</v>
+      </c>
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B9" s="1">
+        <v>45739</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="0"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="C10" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.88472222222222219</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="0"/>
+        <v>9.3055555555555558E-2</v>
+      </c>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="C11" s="2">
+        <v>0.97430555555555554</v>
+      </c>
+      <c r="D11" s="2">
+        <v>7.1527777777777773E-2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" si="0"/>
+        <v>9.7222222222222321E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>45740</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2">
+        <f>IF(D12&lt;C12, D12+1, D12) - C12</f>
+        <v>0.14583333333333337</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="C13" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="D13" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="2">
+        <f>IF(D13&lt;C13, D13+1, D13) - C13</f>
+        <v>7.638888888888884E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>45741</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="2">
+        <f>IF(D14&lt;C14, D14+1, D14) - C14</f>
+        <v>0.15277777777777779</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="C15" s="2">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="2">
+        <f>IF(D15&lt;C15, D15+1, D15) - C15</f>
+        <v>8.3333333333333259E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <v>45742</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="2">
+        <f>IF(D16&lt;C16, D16+1, D16) - C16</f>
+        <v>0.10416666666666663</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <v>45744</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D17" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="2">
+        <f t="shared" ref="G17:G20" si="1">IF(D17&lt;C17, D17+1, D17) - C17</f>
+        <v>0.25000000000000011</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>45745</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="2">
+        <f t="shared" si="1"/>
+        <v>6.2500000000000056E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="2">
+        <f t="shared" si="1"/>
+        <v>0.16666666666666663</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.4375</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="2">
+        <f t="shared" si="1"/>
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C21" s="2">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="D21" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="2">
+        <f t="shared" ref="G21:G27" si="2">IF(D21&lt;C21, D21+1, D21) - C21</f>
+        <v>5.208333333333337E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="B22" s="1">
+        <v>45746</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.61388888888888893</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" s="2">
+        <f t="shared" si="2"/>
+        <v>0.11388888888888893</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="C23" s="2">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.85763888888888884</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="2">
+        <f t="shared" si="2"/>
+        <v>6.597222222222221E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="B24" s="1">
+        <v>45747</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.57291666666666663</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="2"/>
+        <v>9.375E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="C25" s="2">
+        <v>0.75902777777777775</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.79027777777777775</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="2"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="C26" s="2">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.98263888888888884</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="2">
+        <f t="shared" si="2"/>
+        <v>8.6805555555555469E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="C27" s="2">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="D27" s="2">
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="2">
+        <f t="shared" si="2"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="1">
+        <v>45749</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="D28" s="2">
+        <v>0.99305555555555558</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G28" s="2">
+        <f t="shared" ref="G28:G33" si="3">IF(D28&lt;C28, D28+1, D28) - C28</f>
+        <v>3.472222222222221E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="120" x14ac:dyDescent="0.25">
+      <c r="B29" s="1">
+        <v>45750</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.96180555555555558</v>
+      </c>
+      <c r="D29" s="2">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="2">
+        <f t="shared" si="3"/>
+        <v>7.5694444444444509E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B30" s="1">
+        <v>45751</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.72569444444444442</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="2">
+        <f t="shared" si="3"/>
+        <v>3.819444444444442E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="C31" s="2">
+        <v>0.88124999999999998</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.91180555555555554</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="2">
+        <f t="shared" si="3"/>
+        <v>3.0555555555555558E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B32" s="1">
+        <v>45752</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G32" s="2">
+        <f t="shared" si="3"/>
+        <v>0.19791666666666663</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B33" s="1">
+        <v>45753</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.6791666666666667</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="2">
+        <f t="shared" si="3"/>
+        <v>3.7499999999999978E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C0A223-2407-4505-BAD0-756DF8AFB831}">
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -643,7 +1271,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F1" s="5"/>
     </row>
@@ -659,7 +1287,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>3.2833333333333332</v>
+        <v>0.10486111111111113</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -687,511 +1315,179 @@
       </c>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
-        <v>45738</v>
+        <v>45753</v>
       </c>
       <c r="C7" s="2">
-        <v>0.625</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="D7" s="2">
-        <v>0.77430555555555558</v>
+        <v>0.56319444444444444</v>
       </c>
       <c r="E7" t="s">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="G7" s="2">
-        <f t="shared" ref="G7:G11" si="0">IF(D7&lt;C7, D7+1, D7) - C7</f>
-        <v>0.14930555555555558</v>
+        <f t="shared" ref="G7" si="0">IF(D7&lt;C7, D7+1, D7) - C7</f>
+        <v>0.10486111111111113</v>
       </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="2">
-        <v>0.87013888888888891</v>
-      </c>
-      <c r="D8" s="2">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>0.17152777777777783</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="G8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B9" s="1">
-        <v>45739</v>
-      </c>
-      <c r="C9" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="2">
-        <f t="shared" si="0"/>
-        <v>6.25E-2</v>
-      </c>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="1"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="G9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="C10" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D10" s="2">
-        <v>0.88472222222222219</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="2">
-        <f t="shared" si="0"/>
-        <v>9.3055555555555558E-2</v>
-      </c>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="G10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="C11" s="2">
-        <v>0.97430555555555554</v>
-      </c>
-      <c r="D11" s="2">
-        <v>7.1527777777777773E-2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2">
-        <f t="shared" si="0"/>
-        <v>9.7222222222222321E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="1">
-        <v>45740</v>
-      </c>
-      <c r="C12" s="2">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="D12" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="2">
-        <f>IF(D12&lt;C12, D12+1, D12) - C12</f>
-        <v>0.14583333333333337</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="C13" s="2">
-        <v>0.98611111111111116</v>
-      </c>
-      <c r="D13" s="2">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="2">
-        <f>IF(D13&lt;C13, D13+1, D13) - C13</f>
-        <v>7.638888888888884E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="B14" s="1">
-        <v>45741</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0.63888888888888884</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="2">
-        <f>IF(D14&lt;C14, D14+1, D14) - C14</f>
-        <v>0.15277777777777779</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="C15" s="2">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="D15" s="2">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="2">
-        <f>IF(D15&lt;C15, D15+1, D15) - C15</f>
-        <v>8.3333333333333259E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="135" x14ac:dyDescent="0.25">
-      <c r="B16" s="1">
-        <v>45742</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="D16" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="2">
-        <f>IF(D16&lt;C16, D16+1, D16) - C16</f>
-        <v>0.10416666666666663</v>
-      </c>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="G16" s="2"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="1">
-        <v>45744</v>
-      </c>
-      <c r="C17" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D17" s="2">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="2">
-        <f t="shared" ref="G17:G20" si="1">IF(D17&lt;C17, D17+1, D17) - C17</f>
-        <v>0.25000000000000011</v>
-      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="G17" s="2"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="1">
-        <v>45745</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G18" s="2">
-        <f t="shared" si="1"/>
-        <v>6.2500000000000056E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="1"/>
-      <c r="C19" s="2">
-        <v>0.625</v>
-      </c>
-      <c r="D19" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="2">
-        <f t="shared" si="1"/>
-        <v>0.16666666666666663</v>
-      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="G19" s="2"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="1"/>
-      <c r="C20" s="2">
-        <v>0.875</v>
-      </c>
-      <c r="D20" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="2">
-        <f t="shared" si="1"/>
-        <v>0.5625</v>
-      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="G20" s="2"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C21" s="2">
-        <v>0.98958333333333337</v>
-      </c>
-      <c r="D21" s="2">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="2">
-        <f t="shared" ref="G21:G27" si="2">IF(D21&lt;C21, D21+1, D21) - C21</f>
-        <v>5.208333333333337E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="B22" s="1">
-        <v>45746</v>
-      </c>
-      <c r="C22" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.61388888888888893</v>
-      </c>
-      <c r="E22" t="s">
-        <v>1</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="2">
-        <f t="shared" si="2"/>
-        <v>0.11388888888888893</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="C23" s="2">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D23" s="2">
-        <v>0.85763888888888884</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="2">
-        <f t="shared" si="2"/>
-        <v>6.597222222222221E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="B24" s="1">
-        <v>45747</v>
-      </c>
-      <c r="C24" s="2">
-        <v>0.57291666666666663</v>
-      </c>
-      <c r="D24" s="2">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="2">
-        <f t="shared" si="2"/>
-        <v>9.375E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="C25" s="2">
-        <v>0.75902777777777775</v>
-      </c>
-      <c r="D25" s="2">
-        <v>0.79027777777777775</v>
-      </c>
-      <c r="E25" t="s">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="2">
-        <f t="shared" si="2"/>
-        <v>3.125E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="C26" s="2">
-        <v>0.89583333333333337</v>
-      </c>
-      <c r="D26" s="2">
-        <v>0.98263888888888884</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G26" s="2">
-        <f t="shared" si="2"/>
-        <v>8.6805555555555469E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="C27" s="2">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="D27" s="2">
-        <v>3.4722222222222224E-2</v>
-      </c>
-      <c r="E27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G27" s="2">
-        <f t="shared" si="2"/>
-        <v>3.125E-2</v>
-      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="1"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="1"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="G27" s="2"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="1">
-        <v>45749</v>
-      </c>
-      <c r="C28" s="2">
-        <v>0.95833333333333337</v>
-      </c>
-      <c r="D28" s="2">
-        <v>0.99305555555555558</v>
-      </c>
-      <c r="E28" t="s">
-        <v>1</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="2">
-        <f>IF(D28&lt;C28, D28+1, D28) - C28</f>
-        <v>3.472222222222221E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="B29" s="1">
-        <v>45750</v>
-      </c>
-      <c r="C29" s="2">
-        <v>0.96180555555555558</v>
-      </c>
-      <c r="D29" s="2">
-        <v>3.7499999999999999E-2</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="2">
-        <f>IF(D29&lt;C29, D29+1, D29) - C29</f>
-        <v>7.5694444444444509E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B30" s="1">
-        <v>45751</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0.6875</v>
-      </c>
-      <c r="D30" s="2">
-        <v>0.72569444444444442</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="2">
-        <f>IF(D30&lt;C30, D30+1, D30) - C30</f>
-        <v>3.819444444444442E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="C31" s="2">
-        <v>0.88124999999999998</v>
-      </c>
-      <c r="D31" s="2">
-        <v>0.91180555555555554</v>
-      </c>
-      <c r="E31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" s="2">
-        <f>IF(D31&lt;C31, D31+1, D31) - C31</f>
-        <v>3.0555555555555558E-2</v>
-      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="G31" s="2"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="1">
-        <v>45752</v>
-      </c>
-      <c r="C32" s="2">
-        <v>0.54861111111111116</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G32" s="2">
-        <f>IF(D32&lt;C32, D32+1, D32) - C32</f>
-        <v>0.45138888888888884</v>
-      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="G32" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16EBAB43-9BF7-46C1-BE2D-33751923E718}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78873092-0864-4483-A329-02093806C1A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEAD224-1B87-4B31-BA0E-40DABC527693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="735" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -308,8 +308,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G33" totalsRowShown="0">
-  <autoFilter ref="B6:G33" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G34" totalsRowShown="0">
+  <autoFilter ref="B6:G34" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -675,7 +675,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -702,7 +702,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>3.067361111111111</v>
+        <v>3.1701388888888888</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1247,6 +1247,18 @@
       <c r="G33" s="2">
         <f t="shared" si="3"/>
         <v>3.7499999999999978E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C34" s="2">
+        <v>0.89722222222222225</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <f>IF(D34&lt;C34, D34+1, D34) - C34</f>
+        <v>0.10277777777777775</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BEAD224-1B87-4B31-BA0E-40DABC527693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C553CE-29F9-48BD-AA7F-24EB0444079B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1560" yWindow="735" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -197,6 +197,21 @@
   <si>
     <t>Fixed cooldown
 - Issues with certain weapons, e.g. singularity, fire staff</t>
+  </si>
+  <si>
+    <t>Fixed bugs with cooldown/weapons
+- All weapons now working
+- Faster attacks
+- started trying to implement new cooldown UI</t>
+  </si>
+  <si>
+    <t>Need to get slower attacks trialed</t>
+  </si>
+  <si>
+    <t>change UI for cooldown</t>
+  </si>
+  <si>
+    <t>trial adding some new weapons?</t>
   </si>
 </sst>
 </file>
@@ -308,8 +323,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G34" totalsRowShown="0">
-  <autoFilter ref="B6:G34" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G37" totalsRowShown="0">
+  <autoFilter ref="B6:G37" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -675,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -702,7 +717,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G41)</f>
-        <v>3.1701388888888888</v>
+        <v>3.1284722222222223</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1249,16 +1264,52 @@
         <v>3.7499999999999978E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" ht="60" x14ac:dyDescent="0.25">
       <c r="C34" s="2">
         <v>0.89722222222222225</v>
       </c>
+      <c r="D34" s="2">
+        <v>0.95833333333333337</v>
+      </c>
       <c r="E34" t="s">
         <v>1</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="G34" s="2">
         <f>IF(D34&lt;C34, D34+1, D34) - C34</f>
-        <v>0.10277777777777775</v>
+        <v>6.1111111111111116E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C35" s="2"/>
+      <c r="F35" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="2">
+        <f>IF(D35&lt;C35, D35+1, D35) - C35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C36" s="2"/>
+      <c r="F36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G36" s="2">
+        <f>IF(D36&lt;C36, D36+1, D36) - C36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C37" s="2"/>
+      <c r="F37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" s="2">
+        <f>IF(D37&lt;C37, D37+1, D37) - C37</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0C553CE-29F9-48BD-AA7F-24EB0444079B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FA38E0-245D-4B7B-B154-47B680BADBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="735" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="2940" yWindow="2115" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="52">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -208,10 +208,32 @@
     <t>Need to get slower attacks trialed</t>
   </si>
   <si>
-    <t>change UI for cooldown</t>
-  </si>
-  <si>
     <t>trial adding some new weapons?</t>
+  </si>
+  <si>
+    <t>Changed UI for cooldown</t>
+  </si>
+  <si>
+    <t>Weapon System</t>
+  </si>
+  <si>
+    <t>Made some decisions on weapon progression in single player
+- persistent weapon with scaling, and weapon drops that carry over (timed or with limited projectiles)</t>
+  </si>
+  <si>
+    <t>Items/Tarot/Ritual</t>
+  </si>
+  <si>
+    <t>Conceptual work on how system might work</t>
+  </si>
+  <si>
+    <t>Added basic implemention of adding weapon sprites</t>
+  </si>
+  <si>
+    <t>Weapon Sprites</t>
+  </si>
+  <si>
+    <t>Adding Friendly Fire</t>
   </si>
 </sst>
 </file>
@@ -323,8 +345,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G37" totalsRowShown="0">
-  <autoFilter ref="B6:G37" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G44" totalsRowShown="0">
+  <autoFilter ref="B6:G44" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -690,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -716,8 +738,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G41)</f>
-        <v>3.1284722222222223</v>
+        <f>SUM(G7:G45)</f>
+        <v>3.5784722222222221</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1278,37 +1300,153 @@
         <v>41</v>
       </c>
       <c r="G34" s="2">
-        <f>IF(D34&lt;C34, D34+1, D34) - C34</f>
+        <f t="shared" ref="G34:G39" si="4">IF(D34&lt;C34, D34+1, D34) - C34</f>
         <v>6.1111111111111116E-2</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C35" s="2"/>
+      <c r="B35" s="1">
+        <v>45754</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.63541666666666663</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1</v>
+      </c>
       <c r="F35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G35" s="2">
+        <f t="shared" si="4"/>
+        <v>7.2916666666666741E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="1"/>
+      <c r="C36" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" s="2">
+        <f t="shared" si="4"/>
+        <v>0.16666666666666663</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="C37" s="2">
+        <v>0.89097222222222228</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.93055555555555558</v>
+      </c>
+      <c r="E37" t="s">
+        <v>45</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G37" s="2">
+        <f t="shared" si="4"/>
+        <v>3.9583333333333304E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="C38" s="2">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="D38" s="2">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="E38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G38" s="2">
+        <f t="shared" si="4"/>
+        <v>2.0833333333333259E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="1">
+        <v>45755</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.69861111111111107</v>
+      </c>
+      <c r="E39" t="s">
+        <v>45</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39" s="2">
+        <f t="shared" si="4"/>
+        <v>5.2777777777777701E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="1"/>
+      <c r="C40" s="2">
+        <v>0.90277777777777779</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="G40" s="2">
+        <f>IF(D40&lt;C40, D40+1, D40) - C40</f>
+        <v>9.722222222222221E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="1"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="G41" s="2">
+        <f>IF(D41&lt;C41, D41+1, D41) - C41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="1"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="G42" s="2">
+        <f>IF(D42&lt;C42, D42+1, D42) - C42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C43" s="2"/>
+      <c r="F43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="2">
+        <f t="shared" ref="G43:G44" si="5">IF(D43&lt;C43, D43+1, D43) - C43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C44" s="2"/>
+      <c r="F44" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G35" s="2">
-        <f>IF(D35&lt;C35, D35+1, D35) - C35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C36" s="2"/>
-      <c r="F36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G36" s="2">
-        <f>IF(D36&lt;C36, D36+1, D36) - C36</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C37" s="2"/>
-      <c r="F37" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G37" s="2">
-        <f>IF(D37&lt;C37, D37+1, D37) - C37</f>
+      <c r="G44" s="2">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FA38E0-245D-4B7B-B154-47B680BADBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043F9820-2F75-48C5-8F5C-1BD52AB13219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2115" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -234,6 +234,12 @@
   </si>
   <si>
     <t>Adding Friendly Fire</t>
+  </si>
+  <si>
+    <t>Adding Friendly Fire and reordering CSV</t>
+  </si>
+  <si>
+    <t>Added Friendly fire - BUT THE WRONG MECHANIC!!!</t>
   </si>
 </sst>
 </file>
@@ -739,7 +745,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G45)</f>
-        <v>3.5784722222222221</v>
+        <v>3.7680555555555548</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1406,28 +1412,44 @@
       <c r="C40" s="2">
         <v>0.90277777777777779</v>
       </c>
-      <c r="D40" s="2"/>
+      <c r="D40" s="2">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="G40" s="2">
         <f>IF(D40&lt;C40, D40+1, D40) - C40</f>
-        <v>9.722222222222221E-2</v>
+        <v>4.166666666666663E-2</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B41" s="1"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="B41" s="1">
+        <v>45756</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>53</v>
+      </c>
       <c r="G41" s="2">
         <f>IF(D41&lt;C41, D41+1, D41) - C41</f>
-        <v>0</v>
+        <v>9.027777777777779E-2</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="1"/>
-      <c r="C42" s="2"/>
+      <c r="C42" s="2">
+        <v>0.84513888888888888</v>
+      </c>
       <c r="D42" s="2"/>
       <c r="G42" s="2">
         <f>IF(D42&lt;C42, D42+1, D42) - C42</f>
-        <v>0</v>
+        <v>0.15486111111111112</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043F9820-2F75-48C5-8F5C-1BD52AB13219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B69246-6D31-4A24-A326-531A377A8009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="2940" yWindow="2115" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="56">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -240,6 +240,12 @@
   </si>
   <si>
     <t>Added Friendly fire - BUT THE WRONG MECHANIC!!!</t>
+  </si>
+  <si>
+    <t>Added self-damage</t>
+  </si>
+  <si>
+    <t>Looking into JSON storage solution</t>
   </si>
 </sst>
 </file>
@@ -351,8 +357,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G44" totalsRowShown="0">
-  <autoFilter ref="B6:G44" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G46" totalsRowShown="0">
+  <autoFilter ref="B6:G46" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -718,7 +724,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -744,8 +750,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G45)</f>
-        <v>3.7680555555555548</v>
+        <f>SUM(G7:G47)</f>
+        <v>4.0249999999999995</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1446,28 +1452,58 @@
       <c r="C42" s="2">
         <v>0.84513888888888888</v>
       </c>
-      <c r="D42" s="2"/>
+      <c r="D42" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="G42" s="2">
         <f>IF(D42&lt;C42, D42+1, D42) - C42</f>
-        <v>0.15486111111111112</v>
+        <v>9.2361111111111116E-2</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C43" s="2"/>
+      <c r="B43" s="1">
+        <v>45757</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.68055555555555558</v>
+      </c>
+      <c r="D43" s="2"/>
       <c r="F43" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="2">
+        <f>IF(D43&lt;C43, D43+1, D43) - C43</f>
+        <v>0.31944444444444442</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="1"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="G44" s="2">
+        <f>IF(D44&lt;C44, D44+1, D44) - C44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C45" s="2"/>
+      <c r="F45" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G43" s="2">
-        <f t="shared" ref="G43:G44" si="5">IF(D43&lt;C43, D43+1, D43) - C43</f>
+      <c r="G45" s="2">
+        <f t="shared" ref="G45:G46" si="5">IF(D45&lt;C45, D45+1, D45) - C45</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C44" s="2"/>
-      <c r="F44" s="3" t="s">
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C46" s="2"/>
+      <c r="F46" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G46" s="2">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B69246-6D31-4A24-A326-531A377A8009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41044F3-C68E-4269-9428-95B23751C0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2940" yWindow="2115" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="59">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -246,6 +246,15 @@
   </si>
   <si>
     <t>Looking into JSON storage solution</t>
+  </si>
+  <si>
+    <t>Completing JSON setup</t>
+  </si>
+  <si>
+    <t>Completed JSON setup</t>
+  </si>
+  <si>
+    <t>Looking into fixing Singularity bomb</t>
   </si>
 </sst>
 </file>
@@ -278,15 +287,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor theme="6" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -294,11 +309,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6"/>
+      </left>
+      <right style="thin">
+        <color theme="6"/>
+      </right>
+      <top style="thin">
+        <color theme="6"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -311,6 +341,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,8 +393,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G46" totalsRowShown="0">
-  <autoFilter ref="B6:G46" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G47" totalsRowShown="0">
+  <autoFilter ref="B6:G47" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -724,7 +760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -751,7 +787,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G47)</f>
-        <v>4.0249999999999995</v>
+        <v>4.5180555555555557</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1421,6 +1457,9 @@
       <c r="D40" s="2">
         <v>0.94444444444444442</v>
       </c>
+      <c r="E40" t="s">
+        <v>45</v>
+      </c>
       <c r="F40" s="3" t="s">
         <v>52</v>
       </c>
@@ -1438,6 +1477,9 @@
       </c>
       <c r="D41" s="2">
         <v>0.75</v>
+      </c>
+      <c r="E41" t="s">
+        <v>45</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>53</v>
@@ -1455,6 +1497,9 @@
       <c r="D42" s="2">
         <v>0.9375</v>
       </c>
+      <c r="E42" t="s">
+        <v>45</v>
+      </c>
       <c r="F42" s="3" t="s">
         <v>54</v>
       </c>
@@ -1471,6 +1516,9 @@
         <v>0.68055555555555558</v>
       </c>
       <c r="D43" s="2"/>
+      <c r="E43" t="s">
+        <v>45</v>
+      </c>
       <c r="F43" s="3" t="s">
         <v>55</v>
       </c>
@@ -1480,32 +1528,79 @@
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B44" s="1"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="B44" s="1">
+        <v>45758</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D44" s="2">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="E44" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>56</v>
+      </c>
       <c r="G44" s="2">
         <f>IF(D44&lt;C44, D44+1, D44) - C44</f>
-        <v>0</v>
+        <v>0.15972222222222221</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C45" s="2"/>
+      <c r="C45" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D45" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="E45" t="s">
+        <v>45</v>
+      </c>
       <c r="F45" s="3" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G45" s="2">
         <f t="shared" ref="G45:G46" si="5">IF(D45&lt;C45, D45+1, D45) - C45</f>
-        <v>0</v>
+        <v>4.1666666666666741E-2</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C46" s="2"/>
+      <c r="C46" s="2">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D46" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E46" t="s">
+        <v>45</v>
+      </c>
       <c r="F46" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G46" s="2">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4.166666666666663E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C47" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G47" s="2">
+        <f>IF(D47&lt;C47, D47+1, D47) - C47</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F48" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F49" s="9" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A41044F3-C68E-4269-9428-95B23751C0DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8372AD3-B26D-4340-B87B-F937DF64035B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2115" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>Looking into fixing Singularity bomb</t>
+  </si>
+  <si>
+    <t>Level System</t>
+  </si>
+  <si>
+    <t>Starting to think about creating new levels</t>
   </si>
 </sst>
 </file>
@@ -341,10 +347,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -393,8 +399,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G47" totalsRowShown="0">
-  <autoFilter ref="B6:G47" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G48" totalsRowShown="0">
+  <autoFilter ref="B6:G48" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -760,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -786,8 +792,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G47)</f>
-        <v>4.5180555555555557</v>
+        <f>SUM(G7:G48)</f>
+        <v>4.3618055555555557</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1588,18 +1594,50 @@
       <c r="C47" s="2">
         <v>0.75</v>
       </c>
+      <c r="D47" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E47" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="G47" s="2">
         <f>IF(D47&lt;C47, D47+1, D47) - C47</f>
-        <v>0.25</v>
+        <v>6.25E-2</v>
       </c>
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F48" s="8" t="s">
+      <c r="C48" s="2">
+        <v>0.96875</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" t="s">
+        <v>59</v>
+      </c>
+      <c r="G48" s="2">
+        <f>IF(D48&lt;C48, D48+1, D48) - C48</f>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="F51" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F49" s="9" t="s">
+    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="F52" s="9" t="s">
         <v>42</v>
       </c>
     </row>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8372AD3-B26D-4340-B87B-F937DF64035B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980DF8E3-2FFE-4E87-BCFB-815898BDB5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -261,6 +261,20 @@
   </si>
   <si>
     <t>Starting to think about creating new levels</t>
+  </si>
+  <si>
+    <t>Implementing arena system
+- fixed connection between existing scenes to load arenas</t>
+  </si>
+  <si>
+    <t>Created new arena editor system:
+Successfully debugged and fixed the ArenaDatabase singleton loading issue (identified the has_singleton timing quirk and implemented the direct access workaround).
+Correctly integrated the GameManager, ArenaDatabase, and battle_arena scene flow for loading specific arena data.
+Set up and used the arena_capture_tool to save layout data, including dynamic spawn points via Marker2Ds.
+Successfully loaded and tested a second, different arena layout, proving the system's flexibility.
+Defined a solid schema for placeholder TileSet properties to enable rapid functional level design.
+Clarified how to handle backgrounds, parallax, decorations, and UI within this system.
+Discussed potential future AI approaches</t>
   </si>
 </sst>
 </file>
@@ -399,8 +413,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G48" totalsRowShown="0">
-  <autoFilter ref="B6:G48" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G50" totalsRowShown="0">
+  <autoFilter ref="B6:G50" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -792,8 +806,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G48)</f>
-        <v>4.3618055555555557</v>
+        <f>SUM(G7:G50)</f>
+        <v>4.7826388888888882</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1621,22 +1635,51 @@
         <v>3.125E-2</v>
       </c>
     </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="G49" s="2"/>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="G50" s="2"/>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B49" s="1">
+        <v>45759</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.59097222222222223</v>
+      </c>
+      <c r="D49" s="2">
+        <v>0.71666666666666667</v>
+      </c>
+      <c r="E49" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49" s="2">
+        <f>IF(D49&lt;C49, D49+1, D49) - C49</f>
+        <v>0.12569444444444444</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="360" x14ac:dyDescent="0.25">
+      <c r="C50" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="D50" s="2">
+        <v>9.5138888888888884E-2</v>
+      </c>
+      <c r="E50" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" s="2">
+        <f>IF(D50&lt;C50, D50+1, D50) - C50</f>
+        <v>0.29513888888888884</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F51" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
       <c r="F52" s="9" t="s">
         <v>42</v>
       </c>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980DF8E3-2FFE-4E87-BCFB-815898BDB5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F4BE9E-B4E4-4F28-855B-1676D2845E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
-    <sheet name="Card Combiner" sheetId="3" r:id="rId2"/>
-    <sheet name="Godot Learning" sheetId="2" r:id="rId3"/>
+    <sheet name="Name Ideas" sheetId="4" r:id="rId2"/>
+    <sheet name="Card Combiner" sheetId="3" r:id="rId3"/>
+    <sheet name="Godot Learning" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="72">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -275,6 +276,35 @@
 Defined a solid schema for placeholder TileSet properties to enable rapid functional level design.
 Clarified how to handle backgrounds, parallax, decorations, and UI within this system.
 Discussed potential future AI approaches</t>
+  </si>
+  <si>
+    <t>Added Twin-Stick control system 
+- Added bug, player character attacks in wrong direction</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Brainstorming names, etc</t>
+  </si>
+  <si>
+    <t>Name Ideas</t>
+  </si>
+  <si>
+    <t>Descendrum</t>
+  </si>
+  <si>
+    <t>Fixing wrong direction
+- attack styles were reversing direction being given by player and weapon base</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>Bug Fix</t>
+  </si>
+  <si>
+    <t>Creating Arena Select Screen</t>
   </si>
 </sst>
 </file>
@@ -413,8 +443,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G50" totalsRowShown="0">
-  <autoFilter ref="B6:G50" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G55" totalsRowShown="0">
+  <autoFilter ref="B6:G55" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -780,7 +810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -806,8 +836,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G50)</f>
-        <v>4.7826388888888882</v>
+        <f>SUM(G7:G55)</f>
+        <v>5.1701388888888893</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1656,7 +1686,7 @@
         <v>0.12569444444444444</v>
       </c>
     </row>
-    <row r="50" spans="2:7" ht="360" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7" ht="372" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="2">
         <v>0.8</v>
       </c>
@@ -1674,13 +1704,110 @@
         <v>0.29513888888888884</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F51" s="8" t="s">
+    <row r="51" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B51" s="1">
+        <v>45760</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="D51" s="2">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="E51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G51" s="2">
+        <f>IF(D51&lt;C51, D51+1, D51) - C51</f>
+        <v>0.21250000000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C52" s="2">
+        <v>0.7993055555555556</v>
+      </c>
+      <c r="D52" s="2">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="E52" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G52" s="2">
+        <f>IF(D52&lt;C52, D52+1, D52) - C52</f>
+        <v>5.4861111111111027E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="C53" s="2">
+        <v>0.84375</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="E53" t="s">
+        <v>70</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53" s="2">
+        <f>IF(D53&lt;C53, D53+1, D53) - C53</f>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C54" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D54" s="2">
+        <v>0.92361111111111116</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G54" s="2">
+        <f>IF(D54&lt;C54, D54+1, D54) - C54</f>
+        <v>4.861111111111116E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C55" s="2">
+        <v>0.95972222222222225</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="G55" s="2">
+        <f>IF(D55&lt;C55, D55+1, D55) - C55</f>
+        <v>4.0277777777777746E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F59" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F52" s="9" t="s">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F60" s="9" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1694,6 +1821,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79C026B-8D30-4100-A805-D11CB8F29CB9}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C0A223-2407-4505-BAD0-756DF8AFB831}">
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1922,7 +2069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16EBAB43-9BF7-46C1-BE2D-33751923E718}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5F4BE9E-B4E4-4F28-855B-1676D2845E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3307E71F-D078-4D41-969B-4E6DCFD5434D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="73">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -256,9 +256,6 @@
   </si>
   <si>
     <t>Looking into fixing Singularity bomb</t>
-  </si>
-  <si>
-    <t>Level System</t>
   </si>
   <si>
     <t>Starting to think about creating new levels</t>
@@ -305,6 +302,12 @@
   </si>
   <si>
     <t>Creating Arena Select Screen</t>
+  </si>
+  <si>
+    <t>Arena System</t>
+  </si>
+  <si>
+    <t>Melee attack style crashing (something to do with attack_direction and timer? Need to check against other scripts and whole system</t>
   </si>
 </sst>
 </file>
@@ -837,7 +840,7 @@
       </c>
       <c r="D4" s="7">
         <f>SUM(G7:G55)</f>
-        <v>5.1701388888888893</v>
+        <v>5.1888888888888891</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1642,13 +1645,13 @@
         <v>0.8125</v>
       </c>
       <c r="E47" t="s">
+        <v>71</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>60</v>
-      </c>
       <c r="G47" s="2">
-        <f>IF(D47&lt;C47, D47+1, D47) - C47</f>
+        <f t="shared" ref="G47:G55" si="6">IF(D47&lt;C47, D47+1, D47) - C47</f>
         <v>6.25E-2</v>
       </c>
     </row>
@@ -1658,10 +1661,10 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="G48" s="2">
-        <f>IF(D48&lt;C48, D48+1, D48) - C48</f>
+        <f t="shared" si="6"/>
         <v>3.125E-2</v>
       </c>
     </row>
@@ -1676,13 +1679,13 @@
         <v>0.71666666666666667</v>
       </c>
       <c r="E49" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G49" s="2">
-        <f>IF(D49&lt;C49, D49+1, D49) - C49</f>
+        <f t="shared" si="6"/>
         <v>0.12569444444444444</v>
       </c>
     </row>
@@ -1694,13 +1697,13 @@
         <v>9.5138888888888884E-2</v>
       </c>
       <c r="E50" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G50" s="2">
-        <f>IF(D50&lt;C50, D50+1, D50) - C50</f>
+        <f t="shared" si="6"/>
         <v>0.29513888888888884</v>
       </c>
     </row>
@@ -1715,13 +1718,13 @@
         <v>0.77083333333333337</v>
       </c>
       <c r="E51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G51" s="2">
-        <f>IF(D51&lt;C51, D51+1, D51) - C51</f>
+        <f t="shared" si="6"/>
         <v>0.21250000000000002</v>
       </c>
     </row>
@@ -1733,13 +1736,13 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="E52" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="G52" s="2">
-        <f>IF(D52&lt;C52, D52+1, D52) - C52</f>
+        <f t="shared" si="6"/>
         <v>5.4861111111111027E-2</v>
       </c>
     </row>
@@ -1751,13 +1754,13 @@
         <v>0.875</v>
       </c>
       <c r="E53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G53" s="2">
-        <f>IF(D53&lt;C53, D53+1, D53) - C53</f>
+        <f t="shared" si="6"/>
         <v>3.125E-2</v>
       </c>
     </row>
@@ -1768,22 +1771,33 @@
       <c r="D54" s="2">
         <v>0.92361111111111116</v>
       </c>
+      <c r="E54" t="s">
+        <v>71</v>
+      </c>
       <c r="F54" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G54" s="2">
-        <f>IF(D54&lt;C54, D54+1, D54) - C54</f>
+        <f t="shared" si="6"/>
         <v>4.861111111111116E-2</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" ht="45" x14ac:dyDescent="0.25">
       <c r="C55" s="2">
         <v>0.95972222222222225</v>
       </c>
-      <c r="D55" s="2"/>
+      <c r="D55" s="2">
+        <v>1.8749999999999999E-2</v>
+      </c>
+      <c r="E55" t="s">
+        <v>69</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="G55" s="2">
-        <f>IF(D55&lt;C55, D55+1, D55) - C55</f>
-        <v>4.0277777777777746E-2</v>
+        <f t="shared" si="6"/>
+        <v>5.902777777777779E-2</v>
       </c>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.25">
@@ -1827,12 +1841,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3307E71F-D078-4D41-969B-4E6DCFD5434D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3C0581-944B-44DD-A5C8-F00AF92AABE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="75">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -308,6 +308,12 @@
   </si>
   <si>
     <t>Melee attack style crashing (something to do with attack_direction and timer? Need to check against other scripts and whole system</t>
+  </si>
+  <si>
+    <t>Rewrote attack style base and attack styles to centralize player direction, and included collision utils into attack styles</t>
+  </si>
+  <si>
+    <t>Enemy AI</t>
   </si>
 </sst>
 </file>
@@ -446,8 +452,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G55" totalsRowShown="0">
-  <autoFilter ref="B6:G55" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G57" totalsRowShown="0">
+  <autoFilter ref="B6:G57" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -813,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -839,8 +845,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G55)</f>
-        <v>5.1888888888888891</v>
+        <f>SUM(G7:G57)</f>
+        <v>5.5347222222222223</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1800,28 +1806,136 @@
         <v>5.902777777777779E-2</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="G56" s="2"/>
+    <row r="56" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B56" s="1">
+        <v>45761</v>
+      </c>
+      <c r="C56" s="2">
+        <v>0.57638888888888884</v>
+      </c>
+      <c r="D56" s="2">
+        <v>0.61736111111111114</v>
+      </c>
+      <c r="E56" t="s">
+        <v>69</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G56" s="2">
+        <f>IF(D56&lt;C56, D56+1, D56) - C56</f>
+        <v>4.0972222222222299E-2</v>
+      </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C57" s="2"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="2">
+        <v>0.69513888888888886</v>
+      </c>
       <c r="D57" s="2"/>
-      <c r="G57" s="2"/>
+      <c r="E57" t="s">
+        <v>74</v>
+      </c>
+      <c r="G57" s="2">
+        <f>IF(D57&lt;C57, D57+1, D57) - C57</f>
+        <v>0.30486111111111114</v>
+      </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="1"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F59" s="8" t="s">
+      <c r="B59" s="1"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B60" s="1"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B61" s="1"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="G61" s="2"/>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="1"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="G62" s="2"/>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B63" s="1"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B64" s="1"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B65" s="1"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B66" s="1"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B67" s="1"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="1"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="1"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B70" s="1"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F73" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F60" s="9" t="s">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F74" s="9" t="s">
         <v>42</v>
       </c>
     </row>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3C0581-944B-44DD-A5C8-F00AF92AABE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A946C1B4-0E02-47D3-AAA8-1025F4091EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -313,7 +313,24 @@
     <t>Rewrote attack style base and attack styles to centralize player direction, and included collision utils into attack styles</t>
   </si>
   <si>
-    <t>Enemy AI</t>
+    <t>Enemy System</t>
+  </si>
+  <si>
+    <t>Created new Enemy System:
+- Enemy Manager
+- Enemy config
+- Basic Enemy
+- Slime (attempt to create procedural slime enemy)
+- Slime spit</t>
+  </si>
+  <si>
+    <t>Added slithering limb</t>
+  </si>
+  <si>
+    <t>Added more basic enemies:
+- bouncer
+- jumper
+- turret</t>
   </si>
 </sst>
 </file>
@@ -452,8 +469,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G57" totalsRowShown="0">
-  <autoFilter ref="B6:G57" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G60" totalsRowShown="0">
+  <autoFilter ref="B6:G60" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -845,8 +862,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G57)</f>
-        <v>5.5347222222222223</v>
+        <f>SUM(G7:G60)</f>
+        <v>6.1958333333333337</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1827,37 +1844,75 @@
         <v>4.0972222222222299E-2</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" ht="90" x14ac:dyDescent="0.25">
       <c r="B57" s="1"/>
       <c r="C57" s="2">
         <v>0.69513888888888886</v>
       </c>
-      <c r="D57" s="2"/>
+      <c r="D57" s="2">
+        <v>0.92638888888888893</v>
+      </c>
       <c r="E57" t="s">
         <v>74</v>
       </c>
+      <c r="F57" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="G57" s="2">
         <f>IF(D57&lt;C57, D57+1, D57) - C57</f>
-        <v>0.30486111111111114</v>
+        <v>0.23125000000000007</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B58" s="1"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="G58" s="2"/>
+      <c r="B58" s="1">
+        <v>45762</v>
+      </c>
+      <c r="C58" s="2">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="D58" s="2">
+        <v>5.7638888888888892E-2</v>
+      </c>
+      <c r="E58" t="s">
+        <v>74</v>
+      </c>
+      <c r="G58" s="2">
+        <f>IF(D58&lt;C58, D58+1, D58) - C58</f>
+        <v>4.7222222222222228E-2</v>
+      </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B59" s="1"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="G59" s="2"/>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C59" s="2">
+        <v>0.6875</v>
+      </c>
+      <c r="D59" s="2">
+        <v>0.8125</v>
+      </c>
+      <c r="E59" t="s">
+        <v>74</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G59" s="2">
+        <f>IF(D59&lt;C59, D59+1, D59) - C59</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="60" x14ac:dyDescent="0.25">
       <c r="B60" s="1"/>
-      <c r="C60" s="2"/>
+      <c r="C60" s="2">
+        <v>0.4375</v>
+      </c>
       <c r="D60" s="2"/>
-      <c r="G60" s="2"/>
+      <c r="F60" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G60" s="2">
+        <f>IF(D60&lt;C60, D60+1, D60) - C60</f>
+        <v>0.5625</v>
+      </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B61" s="1"/>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A946C1B4-0E02-47D3-AAA8-1025F4091EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5158B3-95D8-41D3-A759-33D4525E7469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="86">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -330,7 +330,34 @@
     <t>Added more basic enemies:
 - bouncer
 - jumper
-- turret</t>
+- turret
+- procedural spider
+- procedural spider 3d
+- carrion beast</t>
+  </si>
+  <si>
+    <t>Trying to fix hitboxes for pull blade and blast hammer</t>
+  </si>
+  <si>
+    <t>Bug fix</t>
+  </si>
+  <si>
+    <t>Fixed hitboxes for pull blade and blast hammer</t>
+  </si>
+  <si>
+    <t>Centralised collisions for weapons</t>
+  </si>
+  <si>
+    <t>Creating a new enemy</t>
+  </si>
+  <si>
+    <t>Descendom</t>
+  </si>
+  <si>
+    <t>Fixing projectile collisions</t>
+  </si>
+  <si>
+    <t>Fixing dagger</t>
   </si>
 </sst>
 </file>
@@ -469,8 +496,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G60" totalsRowShown="0">
-  <autoFilter ref="B6:G60" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G66" totalsRowShown="0">
+  <autoFilter ref="B6:G66" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -862,8 +889,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G60)</f>
-        <v>6.1958333333333337</v>
+        <f>SUM(G7:G66)</f>
+        <v>6.5666666666666664</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -1840,7 +1867,7 @@
         <v>73</v>
       </c>
       <c r="G56" s="2">
-        <f>IF(D56&lt;C56, D56+1, D56) - C56</f>
+        <f t="shared" ref="G56:G65" si="7">IF(D56&lt;C56, D56+1, D56) - C56</f>
         <v>4.0972222222222299E-2</v>
       </c>
     </row>
@@ -1859,7 +1886,7 @@
         <v>75</v>
       </c>
       <c r="G57" s="2">
-        <f>IF(D57&lt;C57, D57+1, D57) - C57</f>
+        <f t="shared" si="7"/>
         <v>0.23125000000000007</v>
       </c>
     </row>
@@ -1877,7 +1904,7 @@
         <v>74</v>
       </c>
       <c r="G58" s="2">
-        <f>IF(D58&lt;C58, D58+1, D58) - C58</f>
+        <f t="shared" si="7"/>
         <v>4.7222222222222228E-2</v>
       </c>
     </row>
@@ -1896,59 +1923,128 @@
         <v>76</v>
       </c>
       <c r="G59" s="2">
-        <f>IF(D59&lt;C59, D59+1, D59) - C59</f>
+        <f t="shared" si="7"/>
         <v>0.125</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7" ht="105" x14ac:dyDescent="0.25">
       <c r="B60" s="1"/>
       <c r="C60" s="2">
-        <v>0.4375</v>
-      </c>
-      <c r="D60" s="2"/>
+        <v>0.9375</v>
+      </c>
+      <c r="D60" s="2">
+        <v>7.2916666666666671E-2</v>
+      </c>
       <c r="F60" s="3" t="s">
         <v>77</v>
       </c>
       <c r="G60" s="2">
-        <f>IF(D60&lt;C60, D60+1, D60) - C60</f>
-        <v>0.5625</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B61" s="1"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="G61" s="2"/>
+        <f t="shared" si="7"/>
+        <v>0.13541666666666674</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B61" s="1">
+        <v>45764</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D61" s="2">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="E61" t="s">
+        <v>69</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G61" s="2">
+        <f t="shared" si="7"/>
+        <v>9.9999999999999978E-2</v>
+      </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B62" s="1"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="G62" s="2"/>
+      <c r="B62" s="1">
+        <v>45765</v>
+      </c>
+      <c r="C62" s="2">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D62" s="2">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="E62" t="s">
+        <v>79</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G62" s="2">
+        <f t="shared" si="7"/>
+        <v>0.14236111111111116</v>
+      </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B63" s="1"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
-      <c r="G63" s="2"/>
+      <c r="E63" t="s">
+        <v>74</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G63" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B64" s="1"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
-      <c r="G64" s="2"/>
+      <c r="E64" t="s">
+        <v>45</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G64" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B65" s="1"/>
-      <c r="C65" s="2"/>
+      <c r="B65" s="1">
+        <v>45766</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="D65" s="2"/>
-      <c r="G65" s="2"/>
+      <c r="E65" t="s">
+        <v>45</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G65" s="2">
+        <f t="shared" si="7"/>
+        <v>0.55555555555555558</v>
+      </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
-      <c r="G66" s="2"/>
+      <c r="F66" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G66" s="2">
+        <f>IF(D66&lt;C66, D66+1, D66) - C66</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
@@ -2005,7 +2101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79C026B-8D30-4100-A805-D11CB8F29CB9}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -2016,6 +2112,11 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5158B3-95D8-41D3-A759-33D4525E7469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50B21B4-C8B9-4A91-BC12-E2A3F6363E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -354,10 +354,31 @@
     <t>Descendom</t>
   </si>
   <si>
-    <t>Fixing projectile collisions</t>
-  </si>
-  <si>
-    <t>Fixing dagger</t>
+    <t>Fixing projectile collisions
+- Fixing dagger</t>
+  </si>
+  <si>
+    <t>Creating enemy navigation system</t>
+  </si>
+  <si>
+    <t>Fixed enemy navigation</t>
+  </si>
+  <si>
+    <t>Began refactoring enemy system</t>
+  </si>
+  <si>
+    <t>Enemies</t>
+  </si>
+  <si>
+    <t>Finished first refactoring of enemy system</t>
+  </si>
+  <si>
+    <t>Added Fodder enemy
+- added zap fodder enemy
+- created centralised weapon system for enemies to prevent references spread out across enemy script</t>
+  </si>
+  <si>
+    <t>Adding weapon system to remaining enemies</t>
   </si>
 </sst>
 </file>
@@ -496,8 +517,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G66" totalsRowShown="0">
-  <autoFilter ref="B6:G66" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G71" totalsRowShown="0">
+  <autoFilter ref="B6:G71" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -889,8 +910,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G66)</f>
-        <v>6.5666666666666664</v>
+        <f>SUM(G7:G71)</f>
+        <v>7.3513888888888888</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -2015,14 +2036,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
         <v>45766</v>
       </c>
       <c r="C65" s="2">
         <v>0.44444444444444442</v>
       </c>
-      <c r="D65" s="2"/>
+      <c r="D65" s="2">
+        <v>0.60416666666666663</v>
+      </c>
       <c r="E65" t="s">
         <v>45</v>
       </c>
@@ -2031,49 +2054,121 @@
       </c>
       <c r="G65" s="2">
         <f t="shared" si="7"/>
-        <v>0.55555555555555558</v>
+        <v>0.15972222222222221</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
+      <c r="C66" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D66" s="2">
+        <v>0.80486111111111114</v>
+      </c>
+      <c r="E66" t="s">
+        <v>74</v>
+      </c>
       <c r="F66" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G66" s="2">
         <f>IF(D66&lt;C66, D66+1, D66) - C66</f>
-        <v>0</v>
+        <v>0.13819444444444451</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="G67" s="2"/>
+      <c r="C67" s="2">
+        <v>0.86805555555555558</v>
+      </c>
+      <c r="D67" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G67" s="2">
+        <f>IF(D67&lt;C67, D67+1, D67) - C67</f>
+        <v>4.8611111111111049E-2</v>
+      </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="G68" s="2"/>
+      <c r="C68" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="D68" s="2">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="E68" t="s">
+        <v>74</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G68" s="2">
+        <f>IF(D68&lt;C68, D68+1, D68) - C68</f>
+        <v>9.027777777777779E-2</v>
+      </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B69" s="1"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="G69" s="2"/>
-    </row>
-    <row r="70" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B69" s="1">
+        <v>45767</v>
+      </c>
+      <c r="C69" s="2">
+        <v>0.65972222222222221</v>
+      </c>
+      <c r="D69" s="2">
+        <v>0.74513888888888891</v>
+      </c>
+      <c r="E69" t="s">
+        <v>74</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G69" s="2">
+        <f>IF(D69&lt;C69, D69+1, D69) - C69</f>
+        <v>8.5416666666666696E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="60" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="G70" s="2"/>
+      <c r="C70" s="2">
+        <v>0.89652777777777781</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.12430555555555556</v>
+      </c>
+      <c r="E70" t="s">
+        <v>88</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G70" s="2">
+        <f>IF(D70&lt;C70, D70+1, D70) - C70</f>
+        <v>0.22777777777777763</v>
+      </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C71" s="2"/>
+      <c r="B71" s="1">
+        <v>45768</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0.40972222222222221</v>
+      </c>
       <c r="D71" s="2"/>
-      <c r="G71" s="2"/>
+      <c r="E71" t="s">
+        <v>88</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G71" s="2">
+        <f>IF(D71&lt;C71, D71+1, D71) - C71</f>
+        <v>0.59027777777777779</v>
+      </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C72" s="2"/>

--- a/SD_WorkLog.xlsx
+++ b/SD_WorkLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adamj\Documents\Game Development\Godot\Smash Dungeon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50B21B4-C8B9-4A91-BC12-E2A3F6363E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613D1195-1830-4B76-A1CD-FA9F9BFDA16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
+    <workbookView xWindow="5295" yWindow="2445" windowWidth="21600" windowHeight="11235" xr2:uid="{F19D98A7-6420-4EF7-85AF-F6CF1D239D63}"/>
   </bookViews>
   <sheets>
     <sheet name="Smash Dungeon" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="97">
   <si>
     <t>Smash Dungeon</t>
   </si>
@@ -379,6 +379,21 @@
   </si>
   <si>
     <t>Adding weapon system to remaining enemies</t>
+  </si>
+  <si>
+    <t>Added arena procedural generation</t>
+  </si>
+  <si>
+    <t>Adding new component enemy</t>
+  </si>
+  <si>
+    <t>Components and component configs</t>
+  </si>
+  <si>
+    <t>Trying to get surface clinger to work</t>
+  </si>
+  <si>
+    <t>Surface Clinger</t>
   </si>
 </sst>
 </file>
@@ -517,8 +532,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G71" totalsRowShown="0">
-  <autoFilter ref="B6:G71" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}" name="Table2" displayName="Table2" ref="B6:G78" totalsRowShown="0">
+  <autoFilter ref="B6:G78" xr:uid="{B1FBB0C8-47CA-4FE8-A951-187DAAFDBA3A}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{9EDA08BC-FC93-4374-BA7A-6AB42BF27608}" name="Date"/>
     <tableColumn id="2" xr3:uid="{E52E82DE-B123-4B3E-8A7E-4FB2C6CEEE64}" name="Start" dataDxfId="8"/>
@@ -884,7 +899,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F0887D6-8664-4804-98D8-EE817E3A6A1B}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -910,8 +925,8 @@
         <v>11</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(G7:G71)</f>
-        <v>7.3513888888888888</v>
+        <f>SUM(G7:G78)</f>
+        <v>8.0201388888888889</v>
       </c>
       <c r="I4" s="2"/>
     </row>
@@ -2072,7 +2087,7 @@
         <v>85</v>
       </c>
       <c r="G66" s="2">
-        <f>IF(D66&lt;C66, D66+1, D66) - C66</f>
+        <f t="shared" ref="G66:G71" si="8">IF(D66&lt;C66, D66+1, D66) - C66</f>
         <v>0.13819444444444451</v>
       </c>
     </row>
@@ -2088,7 +2103,7 @@
         <v>86</v>
       </c>
       <c r="G67" s="2">
-        <f>IF(D67&lt;C67, D67+1, D67) - C67</f>
+        <f t="shared" si="8"/>
         <v>4.8611111111111049E-2</v>
       </c>
     </row>
@@ -2107,7 +2122,7 @@
         <v>87</v>
       </c>
       <c r="G68" s="2">
-        <f>IF(D68&lt;C68, D68+1, D68) - C68</f>
+        <f t="shared" si="8"/>
         <v>9.027777777777779E-2</v>
       </c>
     </row>
@@ -2128,7 +2143,7 @@
         <v>89</v>
       </c>
       <c r="G69" s="2">
-        <f>IF(D69&lt;C69, D69+1, D69) - C69</f>
+        <f t="shared" si="8"/>
         <v>8.5416666666666696E-2</v>
       </c>
     </row>
@@ -2147,7 +2162,7 @@
         <v>90</v>
       </c>
       <c r="G70" s="2">
-        <f>IF(D70&lt;C70, D70+1, D70) - C70</f>
+        <f t="shared" si="8"/>
         <v>0.22777777777777763</v>
       </c>
     </row>
@@ -2158,7 +2173,9 @@
       <c r="C71" s="2">
         <v>0.40972222222222221</v>
       </c>
-      <c r="D71" s="2"/>
+      <c r="D71" s="2">
+        <v>0.44097222222222221</v>
+      </c>
       <c r="E71" t="s">
         <v>88</v>
       </c>
@@ -2166,22 +2183,140 @@
         <v>91</v>
       </c>
       <c r="G71" s="2">
-        <f>IF(D71&lt;C71, D71+1, D71) - C71</f>
-        <v>0.59027777777777779</v>
+        <f t="shared" si="8"/>
+        <v>3.125E-2</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="G72" s="2"/>
+      <c r="C72" s="2">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="D72" s="2">
+        <v>0.625</v>
+      </c>
+      <c r="E72" t="s">
+        <v>71</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G72" s="2">
+        <f>IF(D72&lt;C72, D72+1, D72) - C72</f>
+        <v>0.18402777777777779</v>
+      </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F73" s="8" t="s">
+      <c r="C73" s="2">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D73" s="2">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="E73" t="s">
+        <v>74</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G73" s="2">
+        <f>IF(D73&lt;C73, D73+1, D73) - C73</f>
+        <v>0.10833333333333339</v>
+      </c>
+    </row>
+    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C74" s="2">
+        <v>0.875</v>
+      </c>
+      <c r="D74" s="2">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="E74" t="s">
+        <v>74</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G74" s="2">
+        <f>IF(D74&lt;C74, D74+1, D74) - C74</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C75" s="2">
+        <v>0.99930555555555556</v>
+      </c>
+      <c r="D75" s="2">
+        <v>9.4444444444444442E-2</v>
+      </c>
+      <c r="E75" t="s">
+        <v>74</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G75" s="2">
+        <f>IF(D75&lt;C75, D75+1, D75) - C75</f>
+        <v>9.5138888888888995E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B76" s="1">
+        <v>45769</v>
+      </c>
+      <c r="C76" s="2">
+        <v>0.61041666666666672</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E76" t="s">
+        <v>74</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G76" s="2">
+        <f>IF(D76&lt;C76, D76+1, D76) - C76</f>
+        <v>0.30624999999999991</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C77" s="2">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="D77" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G77" s="2">
+        <f>IF(D77&lt;C77, D77+1, D77) - C77</f>
+        <v>8.333333333333337E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B78" s="1">
+        <v>45770</v>
+      </c>
+      <c r="C78" s="2">
+        <v>0.63263888888888886</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G78" s="2">
+        <f>IF(D78&lt;C78, D78+1, D78) - C78</f>
+        <v>0.36736111111111114</v>
+      </c>
+    </row>
+    <row r="86" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F86" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F74" s="9" t="s">
+    <row r="87" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F87" s="9" t="s">
         <v>42</v>
       </c>
     </row>
